--- a/output/pdf_financials_xlsx/ARTG.xlsx
+++ b/output/pdf_financials_xlsx/ARTG.xlsx
@@ -703,16 +703,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.172309</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.722305</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>3.048855</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>3.548307</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1112,16 +1112,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>7.276889</v>
+        <v>7.10458</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-13.710752</v>
+        <v>-14.433057</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-21.629912</v>
+        <v>-24.678767</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-11.555307</v>
+        <v>-15.103614</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-31.374</v>
@@ -1162,16 +1162,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>7.276889</v>
+        <v>7.10458</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-13.370111</v>
+        <v>-14.092416</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-21.217658</v>
+        <v>-24.266513</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-10.87593</v>
+        <v>-14.424237</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-30.69255</v>
@@ -3543,22 +3543,22 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.03689</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.296529</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.361871</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-1.277934</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-5.621</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-20.65</v>
       </c>
     </row>
     <row r="125">
@@ -3568,22 +3568,22 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.03689</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.296529</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.361871</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>150</v>
+        <v>148.722066</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>315</v>
+        <v>309.379</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-20.65</v>
       </c>
     </row>
     <row r="126">
@@ -9398,7 +9398,11 @@
           <t>Lease payments 9</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -10674,7 +10678,11 @@
           <t>Lease payments 8</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -12024,7 +12032,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -13234,7 +13246,11 @@
           <t>Lease payments $</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E206" s="5" t="n">
         <v>-0.03689</v>
       </c>
@@ -15674,7 +15690,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -17338,7 +17354,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E296" s="5" t="n">
@@ -17572,7 +17588,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E301" s="5" t="n">

--- a/output/pdf_financials_xlsx/ARTG.xlsx
+++ b/output/pdf_financials_xlsx/ARTG.xlsx
@@ -8772,7 +8772,11 @@
           <t>Deferred income tax expense 20</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -12590,7 +12594,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E192" s="5" t="n">
         <v>1.000895</v>
       </c>
